--- a/tables/Supp_Tables_PHI-SensAnalyse.xlsx
+++ b/tables/Supp_Tables_PHI-SensAnalyse.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">country</t>
   </si>
@@ -26,24 +26,12 @@
     <t xml:space="preserve">NCDweight</t>
   </si>
   <si>
-    <t xml:space="preserve">InsuffPol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">insuff_subscale</t>
-  </si>
-  <si>
     <t xml:space="preserve">Austria</t>
   </si>
   <si>
-    <t xml:space="preserve">Alcohol, Tobacco, Unhealthy dietary patterns</t>
-  </si>
-  <si>
     <t xml:space="preserve">Belgium</t>
   </si>
   <si>
-    <t xml:space="preserve">Alcohol, Unhealthy dietary patterns</t>
-  </si>
-  <si>
     <t xml:space="preserve">Czechia</t>
   </si>
   <si>
@@ -56,30 +44,18 @@
     <t xml:space="preserve">Finland</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">France</t>
   </si>
   <si>
-    <t xml:space="preserve">Alcohol</t>
-  </si>
-  <si>
     <t xml:space="preserve">Germany</t>
   </si>
   <si>
     <t xml:space="preserve">Ireland</t>
   </si>
   <si>
-    <t xml:space="preserve">Unhealthy dietary patterns</t>
-  </si>
-  <si>
     <t xml:space="preserve">Latvia</t>
   </si>
   <si>
-    <t xml:space="preserve">Alcohol, Tobacco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lithuania</t>
   </si>
   <si>
@@ -96,9 +72,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tobacco, Unhealthy dietary patterns</t>
   </si>
   <si>
     <t xml:space="preserve">Switzerland</t>
@@ -446,16 +419,10 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
         <v>39</v>
@@ -466,16 +433,10 @@
       <c r="D2" t="n">
         <v>29</v>
       </c>
-      <c r="E2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
         <v>44</v>
@@ -486,16 +447,10 @@
       <c r="D3" t="n">
         <v>40</v>
       </c>
-      <c r="E3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
         <v>47</v>
@@ -506,16 +461,10 @@
       <c r="D4" t="n">
         <v>42</v>
       </c>
-      <c r="E4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n">
         <v>48</v>
@@ -526,16 +475,10 @@
       <c r="D5" t="n">
         <v>39</v>
       </c>
-      <c r="E5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n">
         <v>48</v>
@@ -546,16 +489,10 @@
       <c r="D6" t="n">
         <v>39</v>
       </c>
-      <c r="E6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F6" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>68</v>
@@ -566,16 +503,10 @@
       <c r="D7" t="n">
         <v>61</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
         <v>65</v>
@@ -586,16 +517,10 @@
       <c r="D8" t="n">
         <v>59</v>
       </c>
-      <c r="E8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n">
         <v>38</v>
@@ -606,16 +531,10 @@
       <c r="D9" t="n">
         <v>26</v>
       </c>
-      <c r="E9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F9" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n">
         <v>66</v>
@@ -626,16 +545,10 @@
       <c r="D10" t="n">
         <v>61</v>
       </c>
-      <c r="E10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n">
         <v>53</v>
@@ -646,16 +559,10 @@
       <c r="D11" t="n">
         <v>48</v>
       </c>
-      <c r="E11" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n">
         <v>60</v>
@@ -666,16 +573,10 @@
       <c r="D12" t="n">
         <v>49</v>
       </c>
-      <c r="E12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n">
         <v>38</v>
@@ -686,16 +587,10 @@
       <c r="D13" t="n">
         <v>27</v>
       </c>
-      <c r="E13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F13" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n">
         <v>46</v>
@@ -706,16 +601,10 @@
       <c r="D14" t="n">
         <v>44</v>
       </c>
-      <c r="E14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n">
         <v>64</v>
@@ -726,16 +615,10 @@
       <c r="D15" t="n">
         <v>53</v>
       </c>
-      <c r="E15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F15" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n">
         <v>59</v>
@@ -746,16 +629,10 @@
       <c r="D16" t="n">
         <v>50</v>
       </c>
-      <c r="E16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n">
         <v>54</v>
@@ -766,16 +643,10 @@
       <c r="D17" t="n">
         <v>48</v>
       </c>
-      <c r="E17" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F17" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n">
         <v>33</v>
@@ -786,16 +657,10 @@
       <c r="D18" t="n">
         <v>23</v>
       </c>
-      <c r="E18" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F18" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n">
         <v>73</v>
@@ -805,12 +670,6 @@
       </c>
       <c r="D19" t="n">
         <v>70</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/tables/Supp_Tables_PHI-SensAnalyse.xlsx
+++ b/tables/Supp_Tables_PHI-SensAnalyse.xlsx
@@ -431,7 +431,7 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +473,7 @@
         <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         <v>37</v>
       </c>
       <c r="D6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -501,7 +501,7 @@
         <v>62</v>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
@@ -529,7 +529,7 @@
         <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -543,7 +543,7 @@
         <v>57</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -557,7 +557,7 @@
         <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -571,7 +571,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -585,7 +585,7 @@
         <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -599,7 +599,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -613,7 +613,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -627,7 +627,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
@@ -641,7 +641,7 @@
         <v>49</v>
       </c>
       <c r="D17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
@@ -655,7 +655,7 @@
         <v>22</v>
       </c>
       <c r="D18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
         <v>64</v>
       </c>
       <c r="D19" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
